--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122537858</v>
+        <v>122537920</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>97178</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478971</v>
+        <v>478823</v>
       </c>
       <c r="R2" t="n">
-        <v>6932890</v>
+        <v>6933014</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122539556</v>
+        <v>122536836</v>
       </c>
       <c r="B3" t="n">
-        <v>78652</v>
+        <v>95771</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,16 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478957</v>
+        <v>478988</v>
       </c>
       <c r="R3" t="n">
-        <v>6932890</v>
+        <v>6932854</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122539416</v>
+        <v>122536834</v>
       </c>
       <c r="B4" t="n">
-        <v>79733</v>
+        <v>95771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,16 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>53</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479026</v>
+        <v>478823</v>
       </c>
       <c r="R4" t="n">
-        <v>6932862</v>
+        <v>6933014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122537920</v>
+        <v>122536821</v>
       </c>
       <c r="B5" t="n">
-        <v>97165</v>
+        <v>94626</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,16 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>2809</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1106,7 +1126,7 @@
         <v>122537678</v>
       </c>
       <c r="B6" t="n">
-        <v>82439</v>
+        <v>82443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,6 +1140,11 @@
       </c>
       <c r="E6" t="n">
         <v>1312</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1210,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122539282</v>
+        <v>122537858</v>
       </c>
       <c r="B7" t="n">
-        <v>79768</v>
+        <v>98224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,20 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478856</v>
+        <v>478971</v>
       </c>
       <c r="R7" t="n">
-        <v>6933016</v>
+        <v>6932890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122536836</v>
+        <v>122536835</v>
       </c>
       <c r="B8" t="n">
-        <v>95758</v>
+        <v>95771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1335,6 +1365,11 @@
       <c r="E8" t="n">
         <v>53</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Crossocalyx hellerianus</t>
@@ -1352,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478988</v>
+        <v>478952</v>
       </c>
       <c r="R8" t="n">
-        <v>6932854</v>
+        <v>6932981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122539302</v>
+        <v>122536632</v>
       </c>
       <c r="B9" t="n">
-        <v>79734</v>
+        <v>56593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,20 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478856</v>
+        <v>478870</v>
       </c>
       <c r="R9" t="n">
-        <v>6933016</v>
+        <v>6932903</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122539415</v>
+        <v>122570024</v>
       </c>
       <c r="B10" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,6 +1588,11 @@
       </c>
       <c r="E10" t="n">
         <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1638,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122536821</v>
+        <v>122570132</v>
       </c>
       <c r="B11" t="n">
-        <v>94613</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,16 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>229497</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478823</v>
+        <v>479023</v>
       </c>
       <c r="R11" t="n">
-        <v>6933014</v>
+        <v>6932879</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122539417</v>
+        <v>122570140</v>
       </c>
       <c r="B12" t="n">
-        <v>79733</v>
+        <v>79772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,20 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6463</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478978</v>
+        <v>478856</v>
       </c>
       <c r="R12" t="n">
-        <v>6932862</v>
+        <v>6933016</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122536835</v>
+        <v>122570160</v>
       </c>
       <c r="B13" t="n">
-        <v>95758</v>
+        <v>79738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1868,16 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>2081</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478952</v>
+        <v>478856</v>
       </c>
       <c r="R13" t="n">
-        <v>6932981</v>
+        <v>6933016</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1959,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122539585</v>
+        <v>122570023</v>
       </c>
       <c r="B14" t="n">
-        <v>79600</v>
+        <v>79737</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1971,20 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>385</v>
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1994,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478874</v>
+        <v>478971</v>
       </c>
       <c r="R14" t="n">
-        <v>6933029</v>
+        <v>6932890</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122539586</v>
+        <v>122570130</v>
       </c>
       <c r="B15" t="n">
-        <v>79600</v>
+        <v>79773</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2078,20 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>385</v>
+        <v>6464</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122539274</v>
+        <v>122569853</v>
       </c>
       <c r="B16" t="n">
-        <v>79693</v>
+        <v>79604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2185,20 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>385</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Liten aspgelélav</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2208,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479023</v>
+        <v>478963</v>
       </c>
       <c r="R16" t="n">
-        <v>6932879</v>
+        <v>6932807</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122536834</v>
+        <v>122570141</v>
       </c>
       <c r="B17" t="n">
-        <v>95758</v>
+        <v>79772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,20 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>6463</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2387,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122539412</v>
+        <v>122570119</v>
       </c>
       <c r="B18" t="n">
-        <v>79733</v>
+        <v>79766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2399,20 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2422,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478823</v>
+        <v>478824</v>
       </c>
       <c r="R18" t="n">
-        <v>6933014</v>
+        <v>6933022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122539283</v>
+        <v>122570020</v>
       </c>
       <c r="B19" t="n">
-        <v>79768</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2506,20 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2529,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478823</v>
+        <v>478856</v>
       </c>
       <c r="R19" t="n">
-        <v>6933014</v>
+        <v>6933016</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122539261</v>
+        <v>122570021</v>
       </c>
       <c r="B20" t="n">
-        <v>79762</v>
+        <v>79737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2613,20 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2636,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478824</v>
+        <v>478823</v>
       </c>
       <c r="R20" t="n">
-        <v>6933022</v>
+        <v>6933014</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122539442</v>
+        <v>122570008</v>
       </c>
       <c r="B21" t="n">
-        <v>78652</v>
+        <v>79737</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,16 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2743,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478963</v>
+        <v>478874</v>
       </c>
       <c r="R21" t="n">
-        <v>6932807</v>
+        <v>6933029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2815,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122536632</v>
+        <v>122570142</v>
       </c>
       <c r="B22" t="n">
-        <v>56589</v>
+        <v>79772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2831,16 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>6463</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2850,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478870</v>
+        <v>479039</v>
       </c>
       <c r="R22" t="n">
-        <v>6932903</v>
+        <v>6932861</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2922,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122539272</v>
+        <v>122570025</v>
       </c>
       <c r="B23" t="n">
-        <v>79769</v>
+        <v>79737</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2934,20 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2957,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478963</v>
+        <v>479026</v>
       </c>
       <c r="R23" t="n">
-        <v>6932807</v>
+        <v>6932862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3029,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122539284</v>
+        <v>122570026</v>
       </c>
       <c r="B24" t="n">
-        <v>79768</v>
+        <v>79737</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3041,20 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6463</v>
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3064,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479039</v>
+        <v>478978</v>
       </c>
       <c r="R24" t="n">
-        <v>6932861</v>
+        <v>6932862</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122539414</v>
+        <v>122569852</v>
       </c>
       <c r="B25" t="n">
-        <v>79733</v>
+        <v>79604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3148,20 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>385</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Liten aspgelélav</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478971</v>
+        <v>478874</v>
       </c>
       <c r="R25" t="n">
-        <v>6932890</v>
+        <v>6933029</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3243,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122539411</v>
+        <v>122569957</v>
       </c>
       <c r="B26" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3259,16 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3278,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478856</v>
+        <v>478957</v>
       </c>
       <c r="R26" t="n">
-        <v>6933016</v>
+        <v>6932890</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3350,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122539398</v>
+        <v>122570051</v>
       </c>
       <c r="B27" t="n">
-        <v>79733</v>
+        <v>78656</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3366,16 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122539397</v>
+        <v>122570009</v>
       </c>
       <c r="B28" t="n">
-        <v>79733</v>
+        <v>79737</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3475,6 +3605,11 @@
       <c r="E28" t="n">
         <v>6458</v>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>Lobaria pulmonaria</t>
@@ -3492,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478874</v>
+        <v>478963</v>
       </c>
       <c r="R28" t="n">
-        <v>6933029</v>
+        <v>6932807</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122537920</v>
+        <v>122537678</v>
       </c>
       <c r="B2" t="n">
-        <v>97178</v>
+        <v>82443</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478823</v>
+        <v>478874</v>
       </c>
       <c r="R2" t="n">
-        <v>6933014</v>
+        <v>6933029</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122536836</v>
+        <v>122536834</v>
       </c>
       <c r="B3" t="n">
-        <v>95771</v>
+        <v>95784</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478988</v>
+        <v>478823</v>
       </c>
       <c r="R3" t="n">
-        <v>6932854</v>
+        <v>6933014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122536834</v>
+        <v>122537920</v>
       </c>
       <c r="B4" t="n">
-        <v>95771</v>
+        <v>97191</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122536821</v>
+        <v>122536836</v>
       </c>
       <c r="B5" t="n">
-        <v>94626</v>
+        <v>95784</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478823</v>
+        <v>478988</v>
       </c>
       <c r="R5" t="n">
-        <v>6933014</v>
+        <v>6932854</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122537678</v>
+        <v>122536632</v>
       </c>
       <c r="B6" t="n">
-        <v>82443</v>
+        <v>56593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478874</v>
+        <v>478870</v>
       </c>
       <c r="R6" t="n">
-        <v>6933029</v>
+        <v>6932903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537858</v>
+        <v>122536835</v>
       </c>
       <c r="B7" t="n">
-        <v>98224</v>
+        <v>95784</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478971</v>
+        <v>478952</v>
       </c>
       <c r="R7" t="n">
-        <v>6932890</v>
+        <v>6932981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122536835</v>
+        <v>122537858</v>
       </c>
       <c r="B8" t="n">
-        <v>95771</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478952</v>
+        <v>478971</v>
       </c>
       <c r="R8" t="n">
-        <v>6932981</v>
+        <v>6932890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122536632</v>
+        <v>122536821</v>
       </c>
       <c r="B9" t="n">
-        <v>56593</v>
+        <v>94639</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478870</v>
+        <v>478823</v>
       </c>
       <c r="R9" t="n">
-        <v>6932903</v>
+        <v>6933014</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122570024</v>
+        <v>122570009</v>
       </c>
       <c r="B10" t="n">
         <v>79737</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479039</v>
+        <v>478963</v>
       </c>
       <c r="R10" t="n">
-        <v>6932861</v>
+        <v>6932807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122570132</v>
+        <v>122570025</v>
       </c>
       <c r="B11" t="n">
-        <v>79697</v>
+        <v>79737</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479023</v>
+        <v>479026</v>
       </c>
       <c r="R11" t="n">
-        <v>6932879</v>
+        <v>6932862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122570140</v>
+        <v>122570051</v>
       </c>
       <c r="B12" t="n">
-        <v>79772</v>
+        <v>78656</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,20 +1807,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478856</v>
+        <v>478963</v>
       </c>
       <c r="R12" t="n">
-        <v>6933016</v>
+        <v>6932807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122570160</v>
+        <v>122570142</v>
       </c>
       <c r="B13" t="n">
-        <v>79738</v>
+        <v>79772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478856</v>
+        <v>479039</v>
       </c>
       <c r="R13" t="n">
-        <v>6933016</v>
+        <v>6932861</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122570023</v>
+        <v>122570160</v>
       </c>
       <c r="B14" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478971</v>
+        <v>478856</v>
       </c>
       <c r="R14" t="n">
-        <v>6932890</v>
+        <v>6933016</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122570130</v>
+        <v>122570008</v>
       </c>
       <c r="B15" t="n">
-        <v>79773</v>
+        <v>79737</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478963</v>
+        <v>478874</v>
       </c>
       <c r="R15" t="n">
-        <v>6932807</v>
+        <v>6933029</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122569853</v>
+        <v>122570141</v>
       </c>
       <c r="B16" t="n">
-        <v>79604</v>
+        <v>79772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>385</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478963</v>
+        <v>478823</v>
       </c>
       <c r="R16" t="n">
-        <v>6932807</v>
+        <v>6933014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570141</v>
+        <v>122570024</v>
       </c>
       <c r="B17" t="n">
-        <v>79772</v>
+        <v>79737</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478823</v>
+        <v>479039</v>
       </c>
       <c r="R17" t="n">
-        <v>6933014</v>
+        <v>6932861</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122570119</v>
+        <v>122569852</v>
       </c>
       <c r="B18" t="n">
-        <v>79766</v>
+        <v>79604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>385</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478824</v>
+        <v>478874</v>
       </c>
       <c r="R18" t="n">
-        <v>6933022</v>
+        <v>6933029</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122570020</v>
+        <v>122570132</v>
       </c>
       <c r="B19" t="n">
-        <v>79737</v>
+        <v>79697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478856</v>
+        <v>479023</v>
       </c>
       <c r="R19" t="n">
-        <v>6933016</v>
+        <v>6932879</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122570021</v>
+        <v>122570026</v>
       </c>
       <c r="B20" t="n">
         <v>79737</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478823</v>
+        <v>478978</v>
       </c>
       <c r="R20" t="n">
-        <v>6933014</v>
+        <v>6932862</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122570008</v>
+        <v>122570020</v>
       </c>
       <c r="B21" t="n">
         <v>79737</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478874</v>
+        <v>478856</v>
       </c>
       <c r="R21" t="n">
-        <v>6933029</v>
+        <v>6933016</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122570142</v>
+        <v>122570021</v>
       </c>
       <c r="B22" t="n">
-        <v>79772</v>
+        <v>79737</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,25 +2927,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479039</v>
+        <v>478823</v>
       </c>
       <c r="R22" t="n">
-        <v>6932861</v>
+        <v>6933014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122570025</v>
+        <v>122570140</v>
       </c>
       <c r="B23" t="n">
-        <v>79737</v>
+        <v>79772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479026</v>
+        <v>478856</v>
       </c>
       <c r="R23" t="n">
-        <v>6932862</v>
+        <v>6933016</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122570026</v>
+        <v>122570130</v>
       </c>
       <c r="B24" t="n">
-        <v>79737</v>
+        <v>79773</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478978</v>
+        <v>478963</v>
       </c>
       <c r="R24" t="n">
-        <v>6932862</v>
+        <v>6932807</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122569852</v>
+        <v>122569853</v>
       </c>
       <c r="B25" t="n">
         <v>79604</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478874</v>
+        <v>478963</v>
       </c>
       <c r="R25" t="n">
-        <v>6933029</v>
+        <v>6932807</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122569957</v>
+        <v>122570023</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478957</v>
+        <v>478971</v>
       </c>
       <c r="R26" t="n">
         <v>6932890</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570051</v>
+        <v>122570119</v>
       </c>
       <c r="B27" t="n">
-        <v>78656</v>
+        <v>79766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,25 +3487,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478963</v>
+        <v>478824</v>
       </c>
       <c r="R27" t="n">
-        <v>6932807</v>
+        <v>6933022</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570009</v>
+        <v>122569957</v>
       </c>
       <c r="B28" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478963</v>
+        <v>478957</v>
       </c>
       <c r="R28" t="n">
-        <v>6932807</v>
+        <v>6932890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122537678</v>
+        <v>122536821</v>
       </c>
       <c r="B2" t="n">
-        <v>82443</v>
+        <v>94639</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478874</v>
+        <v>478823</v>
       </c>
       <c r="R2" t="n">
-        <v>6933029</v>
+        <v>6933014</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122536834</v>
+        <v>122536632</v>
       </c>
       <c r="B3" t="n">
-        <v>95784</v>
+        <v>56593</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478823</v>
+        <v>478870</v>
       </c>
       <c r="R3" t="n">
-        <v>6933014</v>
+        <v>6932903</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122536836</v>
+        <v>122536834</v>
       </c>
       <c r="B5" t="n">
         <v>95784</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478988</v>
+        <v>478823</v>
       </c>
       <c r="R5" t="n">
-        <v>6932854</v>
+        <v>6933014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536632</v>
+        <v>122537858</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478870</v>
+        <v>478971</v>
       </c>
       <c r="R6" t="n">
-        <v>6932903</v>
+        <v>6932890</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122537858</v>
+        <v>122537678</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>82443</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478971</v>
+        <v>478874</v>
       </c>
       <c r="R8" t="n">
-        <v>6932890</v>
+        <v>6933029</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122536821</v>
+        <v>122536836</v>
       </c>
       <c r="B9" t="n">
-        <v>94639</v>
+        <v>95784</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478823</v>
+        <v>478988</v>
       </c>
       <c r="R9" t="n">
-        <v>6933014</v>
+        <v>6932854</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122570025</v>
+        <v>122569853</v>
       </c>
       <c r="B11" t="n">
-        <v>79737</v>
+        <v>79604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479026</v>
+        <v>478963</v>
       </c>
       <c r="R11" t="n">
-        <v>6932862</v>
+        <v>6932807</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122570051</v>
+        <v>122570025</v>
       </c>
       <c r="B12" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478963</v>
+        <v>479026</v>
       </c>
       <c r="R12" t="n">
-        <v>6932807</v>
+        <v>6932862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122570142</v>
+        <v>122570130</v>
       </c>
       <c r="B13" t="n">
-        <v>79772</v>
+        <v>79773</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479039</v>
+        <v>478963</v>
       </c>
       <c r="R13" t="n">
-        <v>6932861</v>
+        <v>6932807</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122570160</v>
+        <v>122570008</v>
       </c>
       <c r="B14" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478856</v>
+        <v>478874</v>
       </c>
       <c r="R14" t="n">
-        <v>6933016</v>
+        <v>6933029</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122570008</v>
+        <v>122570119</v>
       </c>
       <c r="B15" t="n">
-        <v>79737</v>
+        <v>79766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478874</v>
+        <v>478824</v>
       </c>
       <c r="R15" t="n">
-        <v>6933029</v>
+        <v>6933022</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122570141</v>
+        <v>122570020</v>
       </c>
       <c r="B16" t="n">
-        <v>79772</v>
+        <v>79737</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478823</v>
+        <v>478856</v>
       </c>
       <c r="R16" t="n">
-        <v>6933014</v>
+        <v>6933016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570024</v>
+        <v>122570140</v>
       </c>
       <c r="B17" t="n">
-        <v>79737</v>
+        <v>79772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479039</v>
+        <v>478856</v>
       </c>
       <c r="R17" t="n">
-        <v>6932861</v>
+        <v>6933016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122569852</v>
+        <v>122569957</v>
       </c>
       <c r="B18" t="n">
-        <v>79604</v>
+        <v>78656</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>385</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478874</v>
+        <v>478957</v>
       </c>
       <c r="R18" t="n">
-        <v>6933029</v>
+        <v>6932890</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122570026</v>
+        <v>122570021</v>
       </c>
       <c r="B20" t="n">
         <v>79737</v>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478978</v>
+        <v>478823</v>
       </c>
       <c r="R20" t="n">
-        <v>6932862</v>
+        <v>6933014</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122570020</v>
+        <v>122570023</v>
       </c>
       <c r="B21" t="n">
         <v>79737</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478856</v>
+        <v>478971</v>
       </c>
       <c r="R21" t="n">
-        <v>6933016</v>
+        <v>6932890</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122570021</v>
+        <v>122570051</v>
       </c>
       <c r="B22" t="n">
-        <v>79737</v>
+        <v>78656</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478823</v>
+        <v>478963</v>
       </c>
       <c r="R22" t="n">
-        <v>6933014</v>
+        <v>6932807</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122570140</v>
+        <v>122570026</v>
       </c>
       <c r="B23" t="n">
-        <v>79772</v>
+        <v>79737</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478856</v>
+        <v>478978</v>
       </c>
       <c r="R23" t="n">
-        <v>6933016</v>
+        <v>6932862</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122570130</v>
+        <v>122570024</v>
       </c>
       <c r="B24" t="n">
-        <v>79773</v>
+        <v>79737</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478963</v>
+        <v>479039</v>
       </c>
       <c r="R24" t="n">
-        <v>6932807</v>
+        <v>6932861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122569853</v>
+        <v>122569852</v>
       </c>
       <c r="B25" t="n">
         <v>79604</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478963</v>
+        <v>478874</v>
       </c>
       <c r="R25" t="n">
-        <v>6932807</v>
+        <v>6933029</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122570023</v>
+        <v>122570160</v>
       </c>
       <c r="B26" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478971</v>
+        <v>478856</v>
       </c>
       <c r="R26" t="n">
-        <v>6932890</v>
+        <v>6933016</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570119</v>
+        <v>122570142</v>
       </c>
       <c r="B27" t="n">
-        <v>79766</v>
+        <v>79772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478824</v>
+        <v>479039</v>
       </c>
       <c r="R27" t="n">
-        <v>6933022</v>
+        <v>6932861</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122569957</v>
+        <v>122570141</v>
       </c>
       <c r="B28" t="n">
-        <v>78656</v>
+        <v>79772</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3599,20 +3599,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478957</v>
+        <v>478823</v>
       </c>
       <c r="R28" t="n">
-        <v>6932890</v>
+        <v>6933014</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122536835</v>
+        <v>122537678</v>
       </c>
       <c r="B7" t="n">
-        <v>95784</v>
+        <v>82443</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478952</v>
+        <v>478874</v>
       </c>
       <c r="R7" t="n">
-        <v>6932981</v>
+        <v>6933029</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122537678</v>
+        <v>122536835</v>
       </c>
       <c r="B8" t="n">
-        <v>82443</v>
+        <v>95784</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1363,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478874</v>
+        <v>478952</v>
       </c>
       <c r="R8" t="n">
-        <v>6933029</v>
+        <v>6932981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122569852</v>
+        <v>122570142</v>
       </c>
       <c r="B25" t="n">
-        <v>79604</v>
+        <v>79772</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>385</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478874</v>
+        <v>479039</v>
       </c>
       <c r="R25" t="n">
-        <v>6933029</v>
+        <v>6932861</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122570160</v>
+        <v>122570141</v>
       </c>
       <c r="B26" t="n">
-        <v>79738</v>
+        <v>79772</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478856</v>
+        <v>478823</v>
       </c>
       <c r="R26" t="n">
-        <v>6933016</v>
+        <v>6933014</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570142</v>
+        <v>122569852</v>
       </c>
       <c r="B27" t="n">
-        <v>79772</v>
+        <v>79604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,25 +3487,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>385</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479039</v>
+        <v>478874</v>
       </c>
       <c r="R27" t="n">
-        <v>6932861</v>
+        <v>6933029</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570141</v>
+        <v>122570160</v>
       </c>
       <c r="B28" t="n">
-        <v>79772</v>
+        <v>79738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3599,25 +3599,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478823</v>
+        <v>478856</v>
       </c>
       <c r="R28" t="n">
-        <v>6933014</v>
+        <v>6933016</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122536821</v>
+        <v>122537678</v>
       </c>
       <c r="B2" t="n">
-        <v>94639</v>
+        <v>82443</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478823</v>
+        <v>478874</v>
       </c>
       <c r="R2" t="n">
-        <v>6933014</v>
+        <v>6933029</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122536632</v>
+        <v>122536836</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>95786</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478870</v>
+        <v>478988</v>
       </c>
       <c r="R3" t="n">
-        <v>6932903</v>
+        <v>6932854</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122537920</v>
+        <v>122536632</v>
       </c>
       <c r="B4" t="n">
-        <v>97191</v>
+        <v>56593</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478823</v>
+        <v>478870</v>
       </c>
       <c r="R4" t="n">
-        <v>6933014</v>
+        <v>6932903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122536834</v>
+        <v>122537920</v>
       </c>
       <c r="B5" t="n">
-        <v>95784</v>
+        <v>97194</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122537858</v>
+        <v>122536821</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>94641</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478971</v>
+        <v>478823</v>
       </c>
       <c r="R6" t="n">
-        <v>6932890</v>
+        <v>6933014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537678</v>
+        <v>122537858</v>
       </c>
       <c r="B7" t="n">
-        <v>82443</v>
+        <v>98240</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478874</v>
+        <v>478971</v>
       </c>
       <c r="R7" t="n">
-        <v>6933029</v>
+        <v>6932890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122536835</v>
+        <v>122536834</v>
       </c>
       <c r="B8" t="n">
-        <v>95784</v>
+        <v>95786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478952</v>
+        <v>478823</v>
       </c>
       <c r="R8" t="n">
-        <v>6932981</v>
+        <v>6933014</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122536836</v>
+        <v>122536835</v>
       </c>
       <c r="B9" t="n">
-        <v>95784</v>
+        <v>95786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478988</v>
+        <v>478952</v>
       </c>
       <c r="R9" t="n">
-        <v>6932854</v>
+        <v>6932981</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122570009</v>
+        <v>122570026</v>
       </c>
       <c r="B10" t="n">
         <v>79737</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478963</v>
+        <v>478978</v>
       </c>
       <c r="R10" t="n">
-        <v>6932807</v>
+        <v>6932862</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122569853</v>
+        <v>122570130</v>
       </c>
       <c r="B11" t="n">
-        <v>79604</v>
+        <v>79773</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>385</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122570025</v>
+        <v>122570024</v>
       </c>
       <c r="B12" t="n">
         <v>79737</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479026</v>
+        <v>479039</v>
       </c>
       <c r="R12" t="n">
-        <v>6932862</v>
+        <v>6932861</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122570130</v>
+        <v>122570160</v>
       </c>
       <c r="B13" t="n">
-        <v>79773</v>
+        <v>79738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478963</v>
+        <v>478856</v>
       </c>
       <c r="R13" t="n">
-        <v>6932807</v>
+        <v>6933016</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122570008</v>
+        <v>122569852</v>
       </c>
       <c r="B14" t="n">
-        <v>79737</v>
+        <v>79604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122570119</v>
+        <v>122570021</v>
       </c>
       <c r="B15" t="n">
-        <v>79766</v>
+        <v>79737</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478824</v>
+        <v>478823</v>
       </c>
       <c r="R15" t="n">
-        <v>6933022</v>
+        <v>6933014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122570020</v>
+        <v>122570119</v>
       </c>
       <c r="B16" t="n">
-        <v>79737</v>
+        <v>79766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478856</v>
+        <v>478824</v>
       </c>
       <c r="R16" t="n">
-        <v>6933016</v>
+        <v>6933022</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570140</v>
+        <v>122570142</v>
       </c>
       <c r="B17" t="n">
         <v>79772</v>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478856</v>
+        <v>479039</v>
       </c>
       <c r="R17" t="n">
-        <v>6933016</v>
+        <v>6932861</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122569957</v>
+        <v>122570023</v>
       </c>
       <c r="B18" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478957</v>
+        <v>478971</v>
       </c>
       <c r="R18" t="n">
         <v>6932890</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122570132</v>
+        <v>122569853</v>
       </c>
       <c r="B19" t="n">
-        <v>79697</v>
+        <v>79604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>385</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479023</v>
+        <v>478963</v>
       </c>
       <c r="R19" t="n">
-        <v>6932879</v>
+        <v>6932807</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122570021</v>
+        <v>122570132</v>
       </c>
       <c r="B20" t="n">
-        <v>79737</v>
+        <v>79697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478823</v>
+        <v>479023</v>
       </c>
       <c r="R20" t="n">
-        <v>6933014</v>
+        <v>6932879</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122570023</v>
+        <v>122570008</v>
       </c>
       <c r="B21" t="n">
         <v>79737</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478971</v>
+        <v>478874</v>
       </c>
       <c r="R21" t="n">
-        <v>6932890</v>
+        <v>6933029</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122570051</v>
+        <v>122570141</v>
       </c>
       <c r="B22" t="n">
-        <v>78656</v>
+        <v>79772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,20 +2927,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478963</v>
+        <v>478823</v>
       </c>
       <c r="R22" t="n">
-        <v>6932807</v>
+        <v>6933014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122570026</v>
+        <v>122570140</v>
       </c>
       <c r="B23" t="n">
-        <v>79737</v>
+        <v>79772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478978</v>
+        <v>478856</v>
       </c>
       <c r="R23" t="n">
-        <v>6932862</v>
+        <v>6933016</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122570024</v>
+        <v>122570009</v>
       </c>
       <c r="B24" t="n">
         <v>79737</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479039</v>
+        <v>478963</v>
       </c>
       <c r="R24" t="n">
-        <v>6932861</v>
+        <v>6932807</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122570142</v>
+        <v>122569957</v>
       </c>
       <c r="B25" t="n">
-        <v>79772</v>
+        <v>78656</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,20 +3263,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479039</v>
+        <v>478957</v>
       </c>
       <c r="R25" t="n">
-        <v>6932861</v>
+        <v>6932890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122570141</v>
+        <v>122570051</v>
       </c>
       <c r="B26" t="n">
-        <v>79772</v>
+        <v>78656</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,20 +3375,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478823</v>
+        <v>478963</v>
       </c>
       <c r="R26" t="n">
-        <v>6933014</v>
+        <v>6932807</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122569852</v>
+        <v>122570025</v>
       </c>
       <c r="B27" t="n">
-        <v>79604</v>
+        <v>79737</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,25 +3487,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478874</v>
+        <v>479026</v>
       </c>
       <c r="R27" t="n">
-        <v>6933029</v>
+        <v>6932862</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570160</v>
+        <v>122570020</v>
       </c>
       <c r="B28" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122537678</v>
+        <v>122536821</v>
       </c>
       <c r="B2" t="n">
-        <v>82443</v>
+        <v>94641</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478874</v>
+        <v>478823</v>
       </c>
       <c r="R2" t="n">
-        <v>6933029</v>
+        <v>6933014</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122536836</v>
+        <v>122537920</v>
       </c>
       <c r="B3" t="n">
-        <v>95786</v>
+        <v>97194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478988</v>
+        <v>478823</v>
       </c>
       <c r="R3" t="n">
-        <v>6932854</v>
+        <v>6933014</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122536632</v>
+        <v>122536835</v>
       </c>
       <c r="B4" t="n">
-        <v>56593</v>
+        <v>95786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478870</v>
+        <v>478952</v>
       </c>
       <c r="R4" t="n">
-        <v>6932903</v>
+        <v>6932981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122537920</v>
+        <v>122537858</v>
       </c>
       <c r="B5" t="n">
-        <v>97194</v>
+        <v>98240</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478823</v>
+        <v>478971</v>
       </c>
       <c r="R5" t="n">
-        <v>6933014</v>
+        <v>6932890</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536821</v>
+        <v>122536632</v>
       </c>
       <c r="B6" t="n">
-        <v>94641</v>
+        <v>56593</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478823</v>
+        <v>478870</v>
       </c>
       <c r="R6" t="n">
-        <v>6933014</v>
+        <v>6932903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537858</v>
+        <v>122536836</v>
       </c>
       <c r="B7" t="n">
-        <v>98240</v>
+        <v>95786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478971</v>
+        <v>478988</v>
       </c>
       <c r="R7" t="n">
-        <v>6932890</v>
+        <v>6932854</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122536835</v>
+        <v>122537678</v>
       </c>
       <c r="B9" t="n">
-        <v>95786</v>
+        <v>82443</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478952</v>
+        <v>478874</v>
       </c>
       <c r="R9" t="n">
-        <v>6932981</v>
+        <v>6933029</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122570026</v>
+        <v>122570142</v>
       </c>
       <c r="B10" t="n">
-        <v>79737</v>
+        <v>79772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478978</v>
+        <v>479039</v>
       </c>
       <c r="R10" t="n">
-        <v>6932862</v>
+        <v>6932861</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122570130</v>
+        <v>122570119</v>
       </c>
       <c r="B11" t="n">
-        <v>79773</v>
+        <v>79766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478963</v>
+        <v>478824</v>
       </c>
       <c r="R11" t="n">
-        <v>6932807</v>
+        <v>6933022</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122570024</v>
+        <v>122570025</v>
       </c>
       <c r="B12" t="n">
         <v>79737</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479039</v>
+        <v>479026</v>
       </c>
       <c r="R12" t="n">
-        <v>6932861</v>
+        <v>6932862</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122570160</v>
+        <v>122570020</v>
       </c>
       <c r="B13" t="n">
-        <v>79738</v>
+        <v>79737</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122569852</v>
+        <v>122570140</v>
       </c>
       <c r="B14" t="n">
-        <v>79604</v>
+        <v>79772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>385</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478874</v>
+        <v>478856</v>
       </c>
       <c r="R14" t="n">
-        <v>6933029</v>
+        <v>6933016</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122570021</v>
+        <v>122570130</v>
       </c>
       <c r="B15" t="n">
-        <v>79737</v>
+        <v>79773</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478823</v>
+        <v>478963</v>
       </c>
       <c r="R15" t="n">
-        <v>6933014</v>
+        <v>6932807</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122570119</v>
+        <v>122570051</v>
       </c>
       <c r="B16" t="n">
-        <v>79766</v>
+        <v>78656</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478824</v>
+        <v>478963</v>
       </c>
       <c r="R16" t="n">
-        <v>6933022</v>
+        <v>6932807</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570142</v>
+        <v>122569957</v>
       </c>
       <c r="B17" t="n">
-        <v>79772</v>
+        <v>78656</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,20 +2367,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479039</v>
+        <v>478957</v>
       </c>
       <c r="R17" t="n">
-        <v>6932861</v>
+        <v>6932890</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122570023</v>
+        <v>122570132</v>
       </c>
       <c r="B18" t="n">
-        <v>79737</v>
+        <v>79697</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478971</v>
+        <v>479023</v>
       </c>
       <c r="R18" t="n">
-        <v>6932890</v>
+        <v>6932879</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122569853</v>
+        <v>122570024</v>
       </c>
       <c r="B19" t="n">
-        <v>79604</v>
+        <v>79737</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478963</v>
+        <v>479039</v>
       </c>
       <c r="R19" t="n">
-        <v>6932807</v>
+        <v>6932861</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122570132</v>
+        <v>122570026</v>
       </c>
       <c r="B20" t="n">
-        <v>79697</v>
+        <v>79737</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479023</v>
+        <v>478978</v>
       </c>
       <c r="R20" t="n">
-        <v>6932879</v>
+        <v>6932862</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122570008</v>
+        <v>122570009</v>
       </c>
       <c r="B21" t="n">
         <v>79737</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478874</v>
+        <v>478963</v>
       </c>
       <c r="R21" t="n">
-        <v>6933029</v>
+        <v>6932807</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122570141</v>
+        <v>122569853</v>
       </c>
       <c r="B22" t="n">
-        <v>79772</v>
+        <v>79604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2927,25 +2927,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>385</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478823</v>
+        <v>478963</v>
       </c>
       <c r="R22" t="n">
-        <v>6933014</v>
+        <v>6932807</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122570140</v>
+        <v>122569852</v>
       </c>
       <c r="B23" t="n">
-        <v>79772</v>
+        <v>79604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>385</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478856</v>
+        <v>478874</v>
       </c>
       <c r="R23" t="n">
-        <v>6933016</v>
+        <v>6933029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122570009</v>
+        <v>122570021</v>
       </c>
       <c r="B24" t="n">
         <v>79737</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478963</v>
+        <v>478823</v>
       </c>
       <c r="R24" t="n">
-        <v>6932807</v>
+        <v>6933014</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122569957</v>
+        <v>122570023</v>
       </c>
       <c r="B25" t="n">
-        <v>78656</v>
+        <v>79737</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,7 +3291,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478957</v>
+        <v>478971</v>
       </c>
       <c r="R25" t="n">
         <v>6932890</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122570051</v>
+        <v>122570141</v>
       </c>
       <c r="B26" t="n">
-        <v>78656</v>
+        <v>79772</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,20 +3375,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478963</v>
+        <v>478823</v>
       </c>
       <c r="R26" t="n">
-        <v>6932807</v>
+        <v>6933014</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570025</v>
+        <v>122570160</v>
       </c>
       <c r="B27" t="n">
-        <v>79737</v>
+        <v>79738</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479026</v>
+        <v>478856</v>
       </c>
       <c r="R27" t="n">
-        <v>6932862</v>
+        <v>6933016</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570020</v>
+        <v>122570008</v>
       </c>
       <c r="B28" t="n">
         <v>79737</v>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478856</v>
+        <v>478874</v>
       </c>
       <c r="R28" t="n">
-        <v>6933016</v>
+        <v>6933029</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>122536834</v>
       </c>
       <c r="B3" t="n">
-        <v>95893</v>
+        <v>95901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>122537678</v>
       </c>
       <c r="B4" t="n">
-        <v>82549</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122537858</v>
+        <v>122536835</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>95901</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478971</v>
+        <v>478952</v>
       </c>
       <c r="R5" t="n">
-        <v>6932890</v>
+        <v>6932981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536835</v>
+        <v>122536836</v>
       </c>
       <c r="B6" t="n">
-        <v>95893</v>
+        <v>95901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478952</v>
+        <v>478988</v>
       </c>
       <c r="R6" t="n">
-        <v>6932981</v>
+        <v>6932854</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1238,7 +1238,7 @@
         <v>122537920</v>
       </c>
       <c r="B7" t="n">
-        <v>97301</v>
+        <v>97309</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122536836</v>
+        <v>122536821</v>
       </c>
       <c r="B8" t="n">
-        <v>95893</v>
+        <v>94756</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478988</v>
+        <v>478823</v>
       </c>
       <c r="R8" t="n">
-        <v>6932854</v>
+        <v>6933014</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122536821</v>
+        <v>122537858</v>
       </c>
       <c r="B9" t="n">
-        <v>94748</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478823</v>
+        <v>478971</v>
       </c>
       <c r="R9" t="n">
-        <v>6933014</v>
+        <v>6932890</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122569853</v>
+        <v>122570009</v>
       </c>
       <c r="B10" t="n">
-        <v>79710</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122570142</v>
+        <v>122570140</v>
       </c>
       <c r="B11" t="n">
-        <v>79878</v>
+        <v>79882</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479039</v>
+        <v>478856</v>
       </c>
       <c r="R11" t="n">
-        <v>6932861</v>
+        <v>6933016</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122570021</v>
+        <v>122570023</v>
       </c>
       <c r="B12" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478823</v>
+        <v>478971</v>
       </c>
       <c r="R12" t="n">
-        <v>6933014</v>
+        <v>6932890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122570009</v>
+        <v>122569853</v>
       </c>
       <c r="B13" t="n">
-        <v>79843</v>
+        <v>79714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122570140</v>
+        <v>122570130</v>
       </c>
       <c r="B14" t="n">
-        <v>79878</v>
+        <v>79883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478856</v>
+        <v>478963</v>
       </c>
       <c r="R14" t="n">
-        <v>6933016</v>
+        <v>6932807</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122570026</v>
+        <v>122570132</v>
       </c>
       <c r="B15" t="n">
-        <v>79843</v>
+        <v>79807</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478978</v>
+        <v>479023</v>
       </c>
       <c r="R15" t="n">
-        <v>6932862</v>
+        <v>6932879</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122570160</v>
+        <v>122570021</v>
       </c>
       <c r="B16" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2259,21 +2259,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478856</v>
+        <v>478823</v>
       </c>
       <c r="R16" t="n">
-        <v>6933016</v>
+        <v>6933014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570119</v>
+        <v>122570025</v>
       </c>
       <c r="B17" t="n">
-        <v>79872</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478824</v>
+        <v>479026</v>
       </c>
       <c r="R17" t="n">
-        <v>6933022</v>
+        <v>6932862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122570008</v>
+        <v>122570119</v>
       </c>
       <c r="B18" t="n">
-        <v>79843</v>
+        <v>79876</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478874</v>
+        <v>478824</v>
       </c>
       <c r="R18" t="n">
-        <v>6933029</v>
+        <v>6933022</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122570024</v>
+        <v>122570142</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>79882</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122570130</v>
+        <v>122569852</v>
       </c>
       <c r="B20" t="n">
-        <v>79879</v>
+        <v>79714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>385</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478963</v>
+        <v>478874</v>
       </c>
       <c r="R20" t="n">
-        <v>6932807</v>
+        <v>6933029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122569852</v>
+        <v>122570020</v>
       </c>
       <c r="B21" t="n">
-        <v>79710</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478874</v>
+        <v>478856</v>
       </c>
       <c r="R21" t="n">
-        <v>6933029</v>
+        <v>6933016</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122569957</v>
+        <v>122570026</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478957</v>
+        <v>478978</v>
       </c>
       <c r="R22" t="n">
-        <v>6932890</v>
+        <v>6932862</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122570132</v>
+        <v>122569957</v>
       </c>
       <c r="B23" t="n">
-        <v>79803</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479023</v>
+        <v>478957</v>
       </c>
       <c r="R23" t="n">
-        <v>6932879</v>
+        <v>6932890</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122570025</v>
+        <v>122570051</v>
       </c>
       <c r="B24" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479026</v>
+        <v>478963</v>
       </c>
       <c r="R24" t="n">
-        <v>6932862</v>
+        <v>6932807</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122570141</v>
+        <v>122570008</v>
       </c>
       <c r="B25" t="n">
-        <v>79878</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3263,25 +3263,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478823</v>
+        <v>478874</v>
       </c>
       <c r="R25" t="n">
-        <v>6933014</v>
+        <v>6933029</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122570051</v>
+        <v>122570160</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>79848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478963</v>
+        <v>478856</v>
       </c>
       <c r="R26" t="n">
-        <v>6932807</v>
+        <v>6933016</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570020</v>
+        <v>122570141</v>
       </c>
       <c r="B27" t="n">
-        <v>79843</v>
+        <v>79882</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,25 +3487,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478856</v>
+        <v>478823</v>
       </c>
       <c r="R27" t="n">
-        <v>6933016</v>
+        <v>6933014</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570023</v>
+        <v>122570024</v>
       </c>
       <c r="B28" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478971</v>
+        <v>479039</v>
       </c>
       <c r="R28" t="n">
-        <v>6932890</v>
+        <v>6932861</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122536834</v>
+        <v>122537920</v>
       </c>
       <c r="B3" t="n">
-        <v>95901</v>
+        <v>97309</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122536835</v>
+        <v>122536834</v>
       </c>
       <c r="B5" t="n">
         <v>95901</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478952</v>
+        <v>478823</v>
       </c>
       <c r="R5" t="n">
-        <v>6932981</v>
+        <v>6933014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536836</v>
+        <v>122536835</v>
       </c>
       <c r="B6" t="n">
         <v>95901</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478988</v>
+        <v>478952</v>
       </c>
       <c r="R6" t="n">
-        <v>6932854</v>
+        <v>6932981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537920</v>
+        <v>122537858</v>
       </c>
       <c r="B7" t="n">
-        <v>97309</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478823</v>
+        <v>478971</v>
       </c>
       <c r="R7" t="n">
-        <v>6933014</v>
+        <v>6932890</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122537858</v>
+        <v>122536836</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>95901</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478971</v>
+        <v>478988</v>
       </c>
       <c r="R9" t="n">
-        <v>6932890</v>
+        <v>6932854</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122570009</v>
+        <v>122570025</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478963</v>
+        <v>479026</v>
       </c>
       <c r="R10" t="n">
-        <v>6932807</v>
+        <v>6932862</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122570140</v>
+        <v>122570119</v>
       </c>
       <c r="B11" t="n">
-        <v>79882</v>
+        <v>79876</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478856</v>
+        <v>478824</v>
       </c>
       <c r="R11" t="n">
-        <v>6933016</v>
+        <v>6933022</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122570023</v>
+        <v>122570021</v>
       </c>
       <c r="B12" t="n">
         <v>79847</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478971</v>
+        <v>478823</v>
       </c>
       <c r="R12" t="n">
-        <v>6932890</v>
+        <v>6933014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122569853</v>
+        <v>122570020</v>
       </c>
       <c r="B13" t="n">
-        <v>79714</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1919,25 +1919,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478963</v>
+        <v>478856</v>
       </c>
       <c r="R13" t="n">
-        <v>6932807</v>
+        <v>6933016</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122570130</v>
+        <v>122569853</v>
       </c>
       <c r="B14" t="n">
-        <v>79883</v>
+        <v>79714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>385</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122570132</v>
+        <v>122569957</v>
       </c>
       <c r="B15" t="n">
-        <v>79807</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2143,25 +2143,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479023</v>
+        <v>478957</v>
       </c>
       <c r="R15" t="n">
-        <v>6932879</v>
+        <v>6932890</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122570021</v>
+        <v>122570132</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478823</v>
+        <v>479023</v>
       </c>
       <c r="R16" t="n">
-        <v>6933014</v>
+        <v>6932879</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570025</v>
+        <v>122570130</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479026</v>
+        <v>478963</v>
       </c>
       <c r="R17" t="n">
-        <v>6932862</v>
+        <v>6932807</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122570119</v>
+        <v>122570160</v>
       </c>
       <c r="B18" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478824</v>
+        <v>478856</v>
       </c>
       <c r="R18" t="n">
-        <v>6933022</v>
+        <v>6933016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122570142</v>
+        <v>122570026</v>
       </c>
       <c r="B19" t="n">
-        <v>79882</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479039</v>
+        <v>478978</v>
       </c>
       <c r="R19" t="n">
-        <v>6932861</v>
+        <v>6932862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122569852</v>
+        <v>122570051</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>385</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478874</v>
+        <v>478963</v>
       </c>
       <c r="R20" t="n">
-        <v>6933029</v>
+        <v>6932807</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122570020</v>
+        <v>122570142</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,25 +2815,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478856</v>
+        <v>479039</v>
       </c>
       <c r="R21" t="n">
-        <v>6933016</v>
+        <v>6932861</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122570026</v>
+        <v>122570008</v>
       </c>
       <c r="B22" t="n">
         <v>79847</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478978</v>
+        <v>478874</v>
       </c>
       <c r="R22" t="n">
-        <v>6932862</v>
+        <v>6933029</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122569957</v>
+        <v>122570141</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79882</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,20 +3039,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478957</v>
+        <v>478823</v>
       </c>
       <c r="R23" t="n">
-        <v>6932890</v>
+        <v>6933014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122570051</v>
+        <v>122570023</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3155,21 +3155,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478963</v>
+        <v>478971</v>
       </c>
       <c r="R24" t="n">
-        <v>6932807</v>
+        <v>6932890</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,7 +3251,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122570008</v>
+        <v>122570009</v>
       </c>
       <c r="B25" t="n">
         <v>79847</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478874</v>
+        <v>478963</v>
       </c>
       <c r="R25" t="n">
-        <v>6933029</v>
+        <v>6932807</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122570160</v>
+        <v>122570024</v>
       </c>
       <c r="B26" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478856</v>
+        <v>479039</v>
       </c>
       <c r="R26" t="n">
-        <v>6933016</v>
+        <v>6932861</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,7 +3475,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570141</v>
+        <v>122570140</v>
       </c>
       <c r="B27" t="n">
         <v>79882</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478823</v>
+        <v>478856</v>
       </c>
       <c r="R27" t="n">
-        <v>6933014</v>
+        <v>6933016</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570024</v>
+        <v>122569852</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>79714</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3599,25 +3599,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479039</v>
+        <v>478874</v>
       </c>
       <c r="R28" t="n">
-        <v>6932861</v>
+        <v>6933029</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122536632</v>
+        <v>122536835</v>
       </c>
       <c r="B2" t="n">
-        <v>56688</v>
+        <v>95903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478870</v>
+        <v>478952</v>
       </c>
       <c r="R2" t="n">
-        <v>6932903</v>
+        <v>6932981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122537920</v>
+        <v>122536836</v>
       </c>
       <c r="B3" t="n">
-        <v>97309</v>
+        <v>95903</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478823</v>
+        <v>478988</v>
       </c>
       <c r="R3" t="n">
-        <v>6933014</v>
+        <v>6932854</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122537678</v>
+        <v>122536834</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
+        <v>95903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478874</v>
+        <v>478823</v>
       </c>
       <c r="R4" t="n">
-        <v>6933029</v>
+        <v>6933014</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122536834</v>
+        <v>122536632</v>
       </c>
       <c r="B5" t="n">
-        <v>95901</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478823</v>
+        <v>478870</v>
       </c>
       <c r="R5" t="n">
-        <v>6933014</v>
+        <v>6932903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536835</v>
+        <v>122537858</v>
       </c>
       <c r="B6" t="n">
-        <v>95901</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478952</v>
+        <v>478971</v>
       </c>
       <c r="R6" t="n">
-        <v>6932981</v>
+        <v>6932890</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537858</v>
+        <v>122536821</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>94758</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478971</v>
+        <v>478823</v>
       </c>
       <c r="R7" t="n">
-        <v>6932890</v>
+        <v>6933014</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122536821</v>
+        <v>122537678</v>
       </c>
       <c r="B8" t="n">
-        <v>94756</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478823</v>
+        <v>478874</v>
       </c>
       <c r="R8" t="n">
-        <v>6933014</v>
+        <v>6933029</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122536836</v>
+        <v>122537920</v>
       </c>
       <c r="B9" t="n">
-        <v>95901</v>
+        <v>97311</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478988</v>
+        <v>478823</v>
       </c>
       <c r="R9" t="n">
-        <v>6932854</v>
+        <v>6933014</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122570025</v>
+        <v>122570130</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1583,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479026</v>
+        <v>478963</v>
       </c>
       <c r="R10" t="n">
-        <v>6932862</v>
+        <v>6932807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122570119</v>
+        <v>122570026</v>
       </c>
       <c r="B11" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478824</v>
+        <v>478978</v>
       </c>
       <c r="R11" t="n">
-        <v>6933022</v>
+        <v>6932862</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122570021</v>
+        <v>122570160</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478823</v>
+        <v>478856</v>
       </c>
       <c r="R12" t="n">
-        <v>6933014</v>
+        <v>6933016</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122570020</v>
+        <v>122570023</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478856</v>
+        <v>478971</v>
       </c>
       <c r="R13" t="n">
-        <v>6933016</v>
+        <v>6932890</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122569853</v>
+        <v>122570009</v>
       </c>
       <c r="B14" t="n">
-        <v>79714</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2031,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122569957</v>
+        <v>122570008</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2147,21 +2147,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478957</v>
+        <v>478874</v>
       </c>
       <c r="R15" t="n">
-        <v>6932890</v>
+        <v>6933029</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570130</v>
+        <v>122570142</v>
       </c>
       <c r="B17" t="n">
-        <v>79883</v>
+        <v>79882</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478963</v>
+        <v>479039</v>
       </c>
       <c r="R17" t="n">
-        <v>6932807</v>
+        <v>6932861</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122570160</v>
+        <v>122570025</v>
       </c>
       <c r="B18" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,21 +2483,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478856</v>
+        <v>479026</v>
       </c>
       <c r="R18" t="n">
-        <v>6933016</v>
+        <v>6932862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122570026</v>
+        <v>122570020</v>
       </c>
       <c r="B19" t="n">
         <v>79847</v>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478978</v>
+        <v>478856</v>
       </c>
       <c r="R19" t="n">
-        <v>6932862</v>
+        <v>6933016</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122570051</v>
+        <v>122570119</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478963</v>
+        <v>478824</v>
       </c>
       <c r="R20" t="n">
-        <v>6932807</v>
+        <v>6933022</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122570142</v>
+        <v>122570141</v>
       </c>
       <c r="B21" t="n">
         <v>79882</v>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479039</v>
+        <v>478823</v>
       </c>
       <c r="R21" t="n">
-        <v>6932861</v>
+        <v>6933014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,7 +2915,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122570008</v>
+        <v>122570024</v>
       </c>
       <c r="B22" t="n">
         <v>79847</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478874</v>
+        <v>479039</v>
       </c>
       <c r="R22" t="n">
-        <v>6933029</v>
+        <v>6932861</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122570141</v>
+        <v>122569853</v>
       </c>
       <c r="B23" t="n">
-        <v>79882</v>
+        <v>79714</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>385</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478823</v>
+        <v>478963</v>
       </c>
       <c r="R23" t="n">
-        <v>6933014</v>
+        <v>6932807</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122570023</v>
+        <v>122569852</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>79714</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478971</v>
+        <v>478874</v>
       </c>
       <c r="R24" t="n">
-        <v>6932890</v>
+        <v>6933029</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122570009</v>
+        <v>122569957</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478963</v>
+        <v>478957</v>
       </c>
       <c r="R25" t="n">
-        <v>6932807</v>
+        <v>6932890</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122570024</v>
+        <v>122570051</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479039</v>
+        <v>478963</v>
       </c>
       <c r="R26" t="n">
-        <v>6932861</v>
+        <v>6932807</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570140</v>
+        <v>122570021</v>
       </c>
       <c r="B27" t="n">
-        <v>79882</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,25 +3487,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478856</v>
+        <v>478823</v>
       </c>
       <c r="R27" t="n">
-        <v>6933016</v>
+        <v>6933014</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122569852</v>
+        <v>122570140</v>
       </c>
       <c r="B28" t="n">
-        <v>79714</v>
+        <v>79882</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3599,25 +3599,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>385</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478874</v>
+        <v>478856</v>
       </c>
       <c r="R28" t="n">
-        <v>6933029</v>
+        <v>6933016</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122536821</v>
+        <v>122537678</v>
       </c>
       <c r="B7" t="n">
-        <v>94758</v>
+        <v>82553</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478823</v>
+        <v>478874</v>
       </c>
       <c r="R7" t="n">
-        <v>6933014</v>
+        <v>6933029</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122537678</v>
+        <v>122536821</v>
       </c>
       <c r="B8" t="n">
-        <v>82553</v>
+        <v>94758</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478874</v>
+        <v>478823</v>
       </c>
       <c r="R8" t="n">
-        <v>6933029</v>
+        <v>6933014</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122536834</v>
+        <v>122537858</v>
       </c>
       <c r="B4" t="n">
-        <v>95903</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478823</v>
+        <v>478971</v>
       </c>
       <c r="R4" t="n">
-        <v>6933014</v>
+        <v>6932890</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122536632</v>
+        <v>122536834</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>95903</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478870</v>
+        <v>478823</v>
       </c>
       <c r="R5" t="n">
-        <v>6932903</v>
+        <v>6933014</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122537858</v>
+        <v>122536632</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>56688</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478971</v>
+        <v>478870</v>
       </c>
       <c r="R6" t="n">
-        <v>6932890</v>
+        <v>6932903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537678</v>
+        <v>122536821</v>
       </c>
       <c r="B7" t="n">
-        <v>82553</v>
+        <v>94758</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478874</v>
+        <v>478823</v>
       </c>
       <c r="R7" t="n">
-        <v>6933029</v>
+        <v>6933014</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122536821</v>
+        <v>122537678</v>
       </c>
       <c r="B8" t="n">
-        <v>94758</v>
+        <v>82553</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478823</v>
+        <v>478874</v>
       </c>
       <c r="R8" t="n">
-        <v>6933014</v>
+        <v>6933029</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122536835</v>
+        <v>122536836</v>
       </c>
       <c r="B2" t="n">
         <v>95903</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478952</v>
+        <v>478988</v>
       </c>
       <c r="R2" t="n">
-        <v>6932981</v>
+        <v>6932854</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122536836</v>
+        <v>122536835</v>
       </c>
       <c r="B3" t="n">
         <v>95903</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478988</v>
+        <v>478952</v>
       </c>
       <c r="R3" t="n">
-        <v>6932854</v>
+        <v>6932981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122537858</v>
+        <v>122537678</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>82553</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478971</v>
+        <v>478874</v>
       </c>
       <c r="R4" t="n">
-        <v>6932890</v>
+        <v>6933029</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122536834</v>
+        <v>122536632</v>
       </c>
       <c r="B5" t="n">
-        <v>95903</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478823</v>
+        <v>478870</v>
       </c>
       <c r="R5" t="n">
-        <v>6933014</v>
+        <v>6932903</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536632</v>
+        <v>122536834</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>95903</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478870</v>
+        <v>478823</v>
       </c>
       <c r="R6" t="n">
-        <v>6932903</v>
+        <v>6933014</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537678</v>
+        <v>122537920</v>
       </c>
       <c r="B7" t="n">
-        <v>82553</v>
+        <v>97311</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478874</v>
+        <v>478823</v>
       </c>
       <c r="R7" t="n">
-        <v>6933029</v>
+        <v>6933014</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122536821</v>
+        <v>122537858</v>
       </c>
       <c r="B8" t="n">
-        <v>94758</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478823</v>
+        <v>478971</v>
       </c>
       <c r="R8" t="n">
-        <v>6933014</v>
+        <v>6932890</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122537920</v>
+        <v>122536821</v>
       </c>
       <c r="B9" t="n">
-        <v>97311</v>
+        <v>94758</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122570130</v>
+        <v>122570141</v>
       </c>
       <c r="B10" t="n">
-        <v>79883</v>
+        <v>79882</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478963</v>
+        <v>478823</v>
       </c>
       <c r="R10" t="n">
-        <v>6932807</v>
+        <v>6933014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122570026</v>
+        <v>122570009</v>
       </c>
       <c r="B11" t="n">
         <v>79847</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478978</v>
+        <v>478963</v>
       </c>
       <c r="R11" t="n">
-        <v>6932862</v>
+        <v>6932807</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122570160</v>
+        <v>122569853</v>
       </c>
       <c r="B12" t="n">
-        <v>79848</v>
+        <v>79714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1807,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>385</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478856</v>
+        <v>478963</v>
       </c>
       <c r="R12" t="n">
-        <v>6933016</v>
+        <v>6932807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122570023</v>
+        <v>122570026</v>
       </c>
       <c r="B13" t="n">
         <v>79847</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478971</v>
+        <v>478978</v>
       </c>
       <c r="R13" t="n">
-        <v>6932890</v>
+        <v>6932862</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122570009</v>
+        <v>122570023</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478963</v>
+        <v>478971</v>
       </c>
       <c r="R14" t="n">
-        <v>6932807</v>
+        <v>6932890</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122570008</v>
+        <v>122570025</v>
       </c>
       <c r="B15" t="n">
         <v>79847</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478874</v>
+        <v>479026</v>
       </c>
       <c r="R15" t="n">
-        <v>6933029</v>
+        <v>6932862</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122570132</v>
+        <v>122570021</v>
       </c>
       <c r="B16" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479023</v>
+        <v>478823</v>
       </c>
       <c r="R16" t="n">
-        <v>6932879</v>
+        <v>6933014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570142</v>
+        <v>122570132</v>
       </c>
       <c r="B17" t="n">
-        <v>79882</v>
+        <v>79807</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,21 +2371,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479039</v>
+        <v>479023</v>
       </c>
       <c r="R17" t="n">
-        <v>6932861</v>
+        <v>6932879</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122570025</v>
+        <v>122570140</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>79882</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479026</v>
+        <v>478856</v>
       </c>
       <c r="R18" t="n">
-        <v>6932862</v>
+        <v>6933016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122570119</v>
+        <v>122569852</v>
       </c>
       <c r="B20" t="n">
-        <v>79876</v>
+        <v>79714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>385</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478824</v>
+        <v>478874</v>
       </c>
       <c r="R20" t="n">
-        <v>6933022</v>
+        <v>6933029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122570141</v>
+        <v>122569957</v>
       </c>
       <c r="B21" t="n">
-        <v>79882</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,20 +2815,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478823</v>
+        <v>478957</v>
       </c>
       <c r="R21" t="n">
-        <v>6933014</v>
+        <v>6932890</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122570024</v>
+        <v>122570051</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479039</v>
+        <v>478963</v>
       </c>
       <c r="R22" t="n">
-        <v>6932861</v>
+        <v>6932807</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122569853</v>
+        <v>122570008</v>
       </c>
       <c r="B23" t="n">
-        <v>79714</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3039,25 +3039,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478963</v>
+        <v>478874</v>
       </c>
       <c r="R23" t="n">
-        <v>6932807</v>
+        <v>6933029</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122569852</v>
+        <v>122570024</v>
       </c>
       <c r="B24" t="n">
-        <v>79714</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,25 +3151,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478874</v>
+        <v>479039</v>
       </c>
       <c r="R24" t="n">
-        <v>6933029</v>
+        <v>6932861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122569957</v>
+        <v>122570160</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478957</v>
+        <v>478856</v>
       </c>
       <c r="R25" t="n">
-        <v>6932890</v>
+        <v>6933016</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122570051</v>
+        <v>122570119</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3375,25 +3375,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478963</v>
+        <v>478824</v>
       </c>
       <c r="R26" t="n">
-        <v>6932807</v>
+        <v>6933022</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570021</v>
+        <v>122570130</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>79883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3487,25 +3487,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478823</v>
+        <v>478963</v>
       </c>
       <c r="R27" t="n">
-        <v>6933014</v>
+        <v>6932807</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,7 +3587,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570140</v>
+        <v>122570142</v>
       </c>
       <c r="B28" t="n">
         <v>79882</v>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478856</v>
+        <v>479039</v>
       </c>
       <c r="R28" t="n">
-        <v>6933016</v>
+        <v>6932861</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -2243,10 +2243,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122570021</v>
+        <v>122570132</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2255,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478823</v>
+        <v>479023</v>
       </c>
       <c r="R16" t="n">
-        <v>6933014</v>
+        <v>6932879</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,10 +2355,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570132</v>
+        <v>122570021</v>
       </c>
       <c r="B17" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2367,25 +2367,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479023</v>
+        <v>478823</v>
       </c>
       <c r="R17" t="n">
-        <v>6932879</v>
+        <v>6933014</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122570020</v>
+        <v>122569852</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>79714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>385</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478856</v>
+        <v>478874</v>
       </c>
       <c r="R19" t="n">
-        <v>6933016</v>
+        <v>6933029</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122569852</v>
+        <v>122569957</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>385</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478874</v>
+        <v>478957</v>
       </c>
       <c r="R20" t="n">
-        <v>6933029</v>
+        <v>6932890</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122569957</v>
+        <v>122570020</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478957</v>
+        <v>478856</v>
       </c>
       <c r="R21" t="n">
-        <v>6932890</v>
+        <v>6933016</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570130</v>
+        <v>122570142</v>
       </c>
       <c r="B27" t="n">
-        <v>79883</v>
+        <v>79882</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478963</v>
+        <v>479039</v>
       </c>
       <c r="R27" t="n">
-        <v>6932807</v>
+        <v>6932861</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570142</v>
+        <v>122570130</v>
       </c>
       <c r="B28" t="n">
-        <v>79882</v>
+        <v>79883</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479039</v>
+        <v>478963</v>
       </c>
       <c r="R28" t="n">
-        <v>6932861</v>
+        <v>6932807</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122569852</v>
+        <v>122570020</v>
       </c>
       <c r="B19" t="n">
-        <v>79714</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2591,25 +2591,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478874</v>
+        <v>478856</v>
       </c>
       <c r="R19" t="n">
-        <v>6933029</v>
+        <v>6933016</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122569957</v>
+        <v>122569852</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2703,25 +2703,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>385</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478957</v>
+        <v>478874</v>
       </c>
       <c r="R20" t="n">
-        <v>6932890</v>
+        <v>6933029</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,10 +2803,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122570020</v>
+        <v>122569957</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,21 +2819,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478856</v>
+        <v>478957</v>
       </c>
       <c r="R21" t="n">
-        <v>6933016</v>
+        <v>6932890</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3475,10 +3475,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570142</v>
+        <v>122570130</v>
       </c>
       <c r="B27" t="n">
-        <v>79882</v>
+        <v>79883</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3491,21 +3491,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479039</v>
+        <v>478963</v>
       </c>
       <c r="R27" t="n">
-        <v>6932861</v>
+        <v>6932807</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570130</v>
+        <v>122570142</v>
       </c>
       <c r="B28" t="n">
-        <v>79883</v>
+        <v>79882</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3603,21 +3603,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>478963</v>
+        <v>479039</v>
       </c>
       <c r="R28" t="n">
-        <v>6932807</v>
+        <v>6932861</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122536836</v>
+        <v>122536834</v>
       </c>
       <c r="B2" t="n">
-        <v>95903</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478988</v>
+        <v>478823</v>
       </c>
       <c r="R2" t="n">
-        <v>6932854</v>
+        <v>6933014</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -790,12 +785,7 @@
         <v>122536835</v>
       </c>
       <c r="B3" t="n">
-        <v>95903</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122537678</v>
+        <v>122536836</v>
       </c>
       <c r="B4" t="n">
-        <v>82553</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478874</v>
+        <v>478988</v>
       </c>
       <c r="R4" t="n">
-        <v>6933029</v>
+        <v>6932854</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122536632</v>
+        <v>122569852</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>385</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478870</v>
+        <v>478874</v>
       </c>
       <c r="R5" t="n">
-        <v>6932903</v>
+        <v>6933029</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122536834</v>
+        <v>122569853</v>
       </c>
       <c r="B6" t="n">
-        <v>95903</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>385</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Liten aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Collema curtisporum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478823</v>
+        <v>478963</v>
       </c>
       <c r="R6" t="n">
-        <v>6933014</v>
+        <v>6932807</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122537920</v>
+        <v>122537678</v>
       </c>
       <c r="B7" t="n">
-        <v>97311</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478823</v>
+        <v>478874</v>
       </c>
       <c r="R7" t="n">
-        <v>6933014</v>
+        <v>6933029</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122537858</v>
+        <v>122570160</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478971</v>
+        <v>478856</v>
       </c>
       <c r="R8" t="n">
-        <v>6932890</v>
+        <v>6933016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,12 +1427,7 @@
         <v>122536821</v>
       </c>
       <c r="B9" t="n">
-        <v>94758</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,32 +1531,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122570141</v>
+        <v>122569957</v>
       </c>
       <c r="B10" t="n">
-        <v>79882</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1611,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478823</v>
+        <v>478957</v>
       </c>
       <c r="R10" t="n">
-        <v>6933014</v>
+        <v>6932890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,37 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122570009</v>
+        <v>122570051</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1795,37 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122569853</v>
+        <v>122570008</v>
       </c>
       <c r="B12" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>385</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478963</v>
+        <v>478874</v>
       </c>
       <c r="R12" t="n">
-        <v>6932807</v>
+        <v>6933029</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,15 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122570026</v>
+        <v>122570009</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478978</v>
+        <v>478963</v>
       </c>
       <c r="R13" t="n">
-        <v>6932862</v>
+        <v>6932807</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,15 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122570023</v>
+        <v>122570020</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478971</v>
+        <v>478856</v>
       </c>
       <c r="R14" t="n">
-        <v>6932890</v>
+        <v>6933016</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,15 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122570025</v>
+        <v>122570021</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2171,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479026</v>
+        <v>478823</v>
       </c>
       <c r="R15" t="n">
-        <v>6932862</v>
+        <v>6933014</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,37 +2173,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122570132</v>
+        <v>122570023</v>
       </c>
       <c r="B16" t="n">
-        <v>79807</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479023</v>
+        <v>478971</v>
       </c>
       <c r="R16" t="n">
-        <v>6932879</v>
+        <v>6932890</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,15 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122570021</v>
+        <v>122570024</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478823</v>
+        <v>479039</v>
       </c>
       <c r="R17" t="n">
-        <v>6933014</v>
+        <v>6932861</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,37 +2387,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122570140</v>
+        <v>122570025</v>
       </c>
       <c r="B18" t="n">
-        <v>79882</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2422,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478856</v>
+        <v>479026</v>
       </c>
       <c r="R18" t="n">
-        <v>6933016</v>
+        <v>6932862</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,15 +2494,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122570020</v>
+        <v>122570026</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2619,10 +2529,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478856</v>
+        <v>478978</v>
       </c>
       <c r="R19" t="n">
-        <v>6933016</v>
+        <v>6932862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,37 +2601,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122569852</v>
+        <v>122570119</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>385</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten aspgelélav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Collema curtisporum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2636,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478874</v>
+        <v>478824</v>
       </c>
       <c r="R20" t="n">
-        <v>6933029</v>
+        <v>6933022</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,32 +2708,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122569957</v>
+        <v>122570140</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2843,10 +2743,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478957</v>
+        <v>478856</v>
       </c>
       <c r="R21" t="n">
-        <v>6932890</v>
+        <v>6933016</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,32 +2815,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122570051</v>
+        <v>122570141</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2955,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478963</v>
+        <v>478823</v>
       </c>
       <c r="R22" t="n">
-        <v>6932807</v>
+        <v>6933014</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,37 +2922,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122570008</v>
+        <v>122570142</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3067,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478874</v>
+        <v>479039</v>
       </c>
       <c r="R23" t="n">
-        <v>6933029</v>
+        <v>6932861</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3139,37 +3029,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122570024</v>
+        <v>122570130</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479039</v>
+        <v>478963</v>
       </c>
       <c r="R24" t="n">
-        <v>6932861</v>
+        <v>6932807</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3251,37 +3136,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122570160</v>
+        <v>122536632</v>
       </c>
       <c r="B25" t="n">
-        <v>79848</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478856</v>
+        <v>478870</v>
       </c>
       <c r="R25" t="n">
-        <v>6933016</v>
+        <v>6932903</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3363,37 +3243,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122570119</v>
+        <v>122537858</v>
       </c>
       <c r="B26" t="n">
-        <v>79876</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3278,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478824</v>
+        <v>478971</v>
       </c>
       <c r="R26" t="n">
-        <v>6933022</v>
+        <v>6932890</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3475,15 +3350,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122570130</v>
+        <v>122537920</v>
       </c>
       <c r="B27" t="n">
-        <v>79883</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,21 +3361,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478963</v>
+        <v>478823</v>
       </c>
       <c r="R27" t="n">
-        <v>6932807</v>
+        <v>6933014</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3587,15 +3457,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122570142</v>
+        <v>122570132</v>
       </c>
       <c r="B28" t="n">
-        <v>79882</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,21 +3468,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3627,10 +3492,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479039</v>
+        <v>479023</v>
       </c>
       <c r="R28" t="n">
-        <v>6932861</v>
+        <v>6932879</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 59023-2021 artfynd.xlsx
+++ b/artfynd/A 59023-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122536834</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122536835</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122536836</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122569852</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122569853</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122537678</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570160</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122536821</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122569957</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570051</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570008</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570009</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570020</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570021</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570023</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570024</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570119</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570140</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570141</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570142</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570130</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122536632</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122537858</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122537920</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,8 +3696,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122570132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>